--- a/agriculture 42.xlsx
+++ b/agriculture 42.xlsx
@@ -20,10 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="88">
-  <si>
-    <t xml:space="preserve">Annual Growtg Rate of State-wise Area Statistics of Coffee in India (1950-2020)</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
   <si>
     <t xml:space="preserve">Year</t>
   </si>
@@ -315,11 +312,12 @@
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="0.00"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -335,14 +333,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -416,16 +406,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -445,23 +431,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -482,988 +468,984 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F83"/>
-  <sheetFormatPr defaultColWidth="10.76953125" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:F1048576"/>
+  <sheetFormatPr defaultColWidth="10.78515625" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="14.42"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="28.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+    <row r="1" customFormat="false" ht="28.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="2" t="s">
+    </row>
+    <row r="2" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
+      <c r="B15" s="3" t="n">
+        <v>33.3333333333333</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>0.942239742326274</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>3.69593447208071</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>430</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>4.34274260898614</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="4" t="n">
-        <v>33.3333333333333</v>
-      </c>
-      <c r="C16" s="5" t="n">
-        <v>0.942239742326274</v>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>3.69593447208071</v>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v>430</v>
-      </c>
-      <c r="F16" s="6" t="n">
-        <v>4.34274260898614</v>
+      <c r="B16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>3.45636385283962</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>4.6768134091128</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>45.2830188679245</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>2.49719865535457</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>3.45636385283962</v>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>4.6768134091128</v>
-      </c>
-      <c r="E17" s="5" t="n">
-        <v>45.2830188679245</v>
-      </c>
-      <c r="F17" s="6" t="n">
-        <v>2.49719865535457</v>
-      </c>
+      <c r="B17" s="3"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="5"/>
     </row>
     <row r="18" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="6"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="5"/>
     </row>
     <row r="19" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="6"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="5"/>
     </row>
     <row r="20" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="4"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="6"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="5"/>
     </row>
     <row r="21" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="6"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="5"/>
     </row>
     <row r="22" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="4"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="6"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="5"/>
     </row>
     <row r="23" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="4"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="6"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="5"/>
     </row>
     <row r="24" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B24" s="4"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="6"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="5"/>
     </row>
     <row r="25" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B25" s="4"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="6"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="5"/>
     </row>
     <row r="26" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B26" s="4"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="6"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="5"/>
     </row>
     <row r="27" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="6"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="5"/>
     </row>
     <row r="28" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B28" s="4"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="6"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="5"/>
     </row>
     <row r="29" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B29" s="4"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="6"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="5"/>
     </row>
     <row r="30" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B30" s="4"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="6"/>
+      <c r="B30" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>0.861244019138756</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>8.70406189555126</v>
+      </c>
+      <c r="E30" s="4"/>
+      <c r="F30" s="5" t="n">
+        <v>-5.47112462006079</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="3" t="s">
+      <c r="A31" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B31" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="C31" s="5" t="n">
-        <v>0.861244019138756</v>
-      </c>
-      <c r="D31" s="5" t="n">
-        <v>8.70406189555126</v>
-      </c>
-      <c r="E31" s="5"/>
-      <c r="F31" s="6" t="n">
-        <v>-5.47112462006079</v>
+      <c r="B31" s="3" t="n">
+        <v>4.16666666666667</v>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>1.80265654648956</v>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>2.49110320284697</v>
+      </c>
+      <c r="E31" s="4"/>
+      <c r="F31" s="5" t="n">
+        <v>0.321543408360129</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B32" s="4" t="n">
-        <v>4.16666666666667</v>
-      </c>
-      <c r="C32" s="5" t="n">
-        <v>1.80265654648956</v>
-      </c>
-      <c r="D32" s="5" t="n">
-        <v>2.49110320284697</v>
-      </c>
-      <c r="E32" s="5"/>
-      <c r="F32" s="6" t="n">
-        <v>0.321543408360129</v>
+      <c r="B32" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>5.31220876048462</v>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>0.520833333333333</v>
+      </c>
+      <c r="E32" s="4"/>
+      <c r="F32" s="5" t="n">
+        <v>5.12820512820513</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="3" t="s">
+      <c r="A33" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B33" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="C33" s="5" t="n">
-        <v>5.31220876048462</v>
-      </c>
-      <c r="D33" s="5" t="n">
-        <v>0.520833333333333</v>
-      </c>
-      <c r="E33" s="5"/>
-      <c r="F33" s="6" t="n">
-        <v>5.12820512820513</v>
+      <c r="B33" s="3" t="n">
+        <v>83.8709677419355</v>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>1.76991150442478</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="4"/>
+      <c r="F33" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="3" t="s">
+      <c r="A34" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B34" s="4" t="n">
-        <v>83.8709677419355</v>
-      </c>
-      <c r="C34" s="5" t="n">
-        <v>1.76991150442478</v>
-      </c>
-      <c r="D34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="5"/>
-      <c r="F34" s="6" t="n">
-        <v>0</v>
+      <c r="B34" s="3" t="n">
+        <v>1.75438596491228</v>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>4.26086956521739</v>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>7.7720207253886</v>
+      </c>
+      <c r="E34" s="4"/>
+      <c r="F34" s="5" t="n">
+        <v>-1.21951219512195</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="3" t="s">
+      <c r="A35" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B35" s="4" t="n">
-        <v>1.75438596491228</v>
-      </c>
-      <c r="C35" s="5" t="n">
-        <v>4.26086956521739</v>
-      </c>
-      <c r="D35" s="5" t="n">
-        <v>7.7720207253886</v>
-      </c>
-      <c r="E35" s="5"/>
-      <c r="F35" s="6" t="n">
-        <v>-1.21951219512195</v>
+      <c r="B35" s="3" t="n">
+        <v>27.5862068965517</v>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>2.50208507089241</v>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>2.56410256410256</v>
+      </c>
+      <c r="E35" s="4"/>
+      <c r="F35" s="5" t="n">
+        <v>-2.46913580246914</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="3" t="s">
+      <c r="A36" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B36" s="4" t="n">
-        <v>27.5862068965517</v>
-      </c>
-      <c r="C36" s="5" t="n">
-        <v>2.50208507089241</v>
-      </c>
-      <c r="D36" s="5" t="n">
-        <v>2.56410256410256</v>
-      </c>
-      <c r="E36" s="5"/>
-      <c r="F36" s="6" t="n">
-        <v>-2.46913580246914</v>
+      <c r="B36" s="3" t="n">
+        <v>4.05405405405405</v>
+      </c>
+      <c r="C36" s="4" t="n">
+        <v>0.895036615134255</v>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E36" s="4"/>
+      <c r="F36" s="5" t="n">
+        <v>-2.84810126582278</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="3" t="s">
+      <c r="A37" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B37" s="4" t="n">
-        <v>4.05405405405405</v>
-      </c>
-      <c r="C37" s="5" t="n">
-        <v>0.895036615134255</v>
-      </c>
-      <c r="D37" s="5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E37" s="5"/>
-      <c r="F37" s="6" t="n">
-        <v>-2.84810126582278</v>
+      <c r="B37" s="3" t="n">
+        <v>-1.2987012987013</v>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>3.14516129032258</v>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="4"/>
+      <c r="F37" s="5" t="n">
+        <v>7.16612377850163</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="3" t="s">
+      <c r="A38" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B38" s="4" t="n">
-        <v>-1.2987012987013</v>
-      </c>
-      <c r="C38" s="5" t="n">
-        <v>3.14516129032258</v>
-      </c>
-      <c r="D38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="5"/>
-      <c r="F38" s="6" t="n">
-        <v>7.16612377850163</v>
+      <c r="B38" s="3" t="n">
+        <v>2.63157894736842</v>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>0.234558248631744</v>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="4"/>
+      <c r="F38" s="5" t="n">
+        <v>1.51975683890578</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="3" t="s">
+      <c r="A39" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B39" s="4" t="n">
-        <v>2.63157894736842</v>
-      </c>
-      <c r="C39" s="5" t="n">
-        <v>0.234558248631744</v>
-      </c>
-      <c r="D39" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" s="5"/>
-      <c r="F39" s="6" t="n">
-        <v>1.51975683890578</v>
+      <c r="B39" s="3" t="n">
+        <v>-6.41025641025641</v>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>-1.40405616224649</v>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>4.11585365853659</v>
+      </c>
+      <c r="E39" s="4"/>
+      <c r="F39" s="5" t="n">
+        <v>-1.79640718562874</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="3" t="s">
+      <c r="A40" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B40" s="4" t="n">
-        <v>-6.41025641025641</v>
-      </c>
-      <c r="C40" s="5" t="n">
-        <v>-1.40405616224649</v>
-      </c>
-      <c r="D40" s="5" t="n">
-        <v>4.11585365853659</v>
-      </c>
-      <c r="E40" s="5"/>
-      <c r="F40" s="6" t="n">
-        <v>-1.79640718562874</v>
+      <c r="B40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>-4.82594936708861</v>
+      </c>
+      <c r="D40" s="4" t="n">
+        <v>11.8594436310395</v>
+      </c>
+      <c r="E40" s="4"/>
+      <c r="F40" s="5" t="n">
+        <v>-3.04878048780488</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="3" t="s">
+      <c r="A41" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C41" s="5" t="n">
-        <v>-4.82594936708861</v>
-      </c>
-      <c r="D41" s="5" t="n">
-        <v>11.8594436310395</v>
-      </c>
-      <c r="E41" s="5"/>
-      <c r="F41" s="6" t="n">
-        <v>-3.04878048780488</v>
+      <c r="B41" s="3" t="n">
+        <v>24.6575342465753</v>
+      </c>
+      <c r="C41" s="4" t="n">
+        <v>-1.74563591022444</v>
+      </c>
+      <c r="D41" s="4" t="n">
+        <v>-2.09424083769633</v>
+      </c>
+      <c r="E41" s="4"/>
+      <c r="F41" s="5" t="n">
+        <v>0.628930817610063</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="3" t="s">
+      <c r="A42" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B42" s="4" t="n">
-        <v>24.6575342465753</v>
-      </c>
-      <c r="C42" s="5" t="n">
-        <v>-1.74563591022444</v>
-      </c>
-      <c r="D42" s="5" t="n">
-        <v>-2.09424083769633</v>
-      </c>
-      <c r="E42" s="5"/>
-      <c r="F42" s="6" t="n">
-        <v>0.628930817610063</v>
+      <c r="B42" s="3" t="n">
+        <v>2.1978021978022</v>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>12.2673434856176</v>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>12.2994652406417</v>
+      </c>
+      <c r="E42" s="4"/>
+      <c r="F42" s="5" t="n">
+        <v>0.625</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="3" t="s">
+      <c r="A43" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B43" s="4" t="n">
-        <v>2.1978021978022</v>
-      </c>
-      <c r="C43" s="5" t="n">
-        <v>12.2673434856176</v>
-      </c>
-      <c r="D43" s="5" t="n">
-        <v>12.2994652406417</v>
-      </c>
-      <c r="E43" s="5"/>
-      <c r="F43" s="6" t="n">
-        <v>0.625</v>
-      </c>
+      <c r="B43" s="3"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="5"/>
     </row>
     <row r="44" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="3" t="s">
+      <c r="A44" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B44" s="4"/>
-      <c r="C44" s="5"/>
-      <c r="D44" s="5"/>
-      <c r="E44" s="5"/>
-      <c r="F44" s="6"/>
+      <c r="B44" s="3"/>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="5"/>
     </row>
     <row r="45" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="3" t="s">
+      <c r="A45" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B45" s="4"/>
-      <c r="C45" s="5"/>
-      <c r="D45" s="5"/>
-      <c r="E45" s="5"/>
-      <c r="F45" s="6"/>
+      <c r="B45" s="3"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="5"/>
     </row>
     <row r="46" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="3" t="s">
+      <c r="A46" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B46" s="4"/>
-      <c r="C46" s="5"/>
-      <c r="D46" s="5"/>
-      <c r="E46" s="5"/>
-      <c r="F46" s="6"/>
+      <c r="B46" s="3"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="5"/>
     </row>
     <row r="47" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="3" t="s">
+      <c r="A47" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B47" s="4"/>
-      <c r="C47" s="5"/>
-      <c r="D47" s="5"/>
-      <c r="E47" s="5"/>
-      <c r="F47" s="6"/>
+      <c r="B47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="4" t="n">
+        <v>7.70700636942675</v>
+      </c>
+      <c r="D47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="4"/>
+      <c r="F47" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="3" t="s">
+      <c r="A48" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B48" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C48" s="5" t="n">
-        <v>7.70700636942675</v>
-      </c>
-      <c r="D48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" s="5"/>
-      <c r="F48" s="6" t="n">
-        <v>0</v>
+      <c r="B48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="4" t="n">
+        <v>0.295683027794205</v>
+      </c>
+      <c r="D48" s="4" t="n">
+        <v>0.364520048602673</v>
+      </c>
+      <c r="E48" s="4"/>
+      <c r="F48" s="5" t="n">
+        <v>-6.40243902439024</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="3" t="s">
+      <c r="A49" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C49" s="5" t="n">
-        <v>0.295683027794205</v>
-      </c>
-      <c r="D49" s="5" t="n">
-        <v>0.364520048602673</v>
-      </c>
-      <c r="E49" s="5"/>
-      <c r="F49" s="6" t="n">
-        <v>-6.40243902439024</v>
+      <c r="B49" s="3"/>
+      <c r="C49" s="4"/>
+      <c r="D49" s="4"/>
+      <c r="E49" s="4"/>
+      <c r="F49" s="5" t="n">
+        <v>-100</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="3" t="s">
+      <c r="A50" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B50" s="4"/>
-      <c r="C50" s="5"/>
-      <c r="D50" s="5"/>
-      <c r="E50" s="5"/>
-      <c r="F50" s="6" t="n">
-        <v>-100</v>
-      </c>
+      <c r="B50" s="3"/>
+      <c r="C50" s="4"/>
+      <c r="D50" s="4"/>
+      <c r="E50" s="4"/>
+      <c r="F50" s="5"/>
     </row>
     <row r="51" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="3" t="s">
+      <c r="A51" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B51" s="4"/>
-      <c r="C51" s="5"/>
-      <c r="D51" s="5"/>
-      <c r="E51" s="5"/>
-      <c r="F51" s="6"/>
+      <c r="B51" s="3"/>
+      <c r="C51" s="4"/>
+      <c r="D51" s="4"/>
+      <c r="E51" s="4"/>
+      <c r="F51" s="5"/>
     </row>
     <row r="52" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="3" t="s">
+      <c r="A52" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B52" s="4"/>
-      <c r="C52" s="5"/>
-      <c r="D52" s="5"/>
-      <c r="E52" s="5"/>
-      <c r="F52" s="6"/>
+      <c r="B52" s="3"/>
+      <c r="C52" s="4"/>
+      <c r="D52" s="4"/>
+      <c r="E52" s="4"/>
+      <c r="F52" s="5"/>
     </row>
     <row r="53" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="3" t="s">
+      <c r="A53" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B53" s="4"/>
-      <c r="C53" s="5"/>
-      <c r="D53" s="5"/>
-      <c r="E53" s="5"/>
-      <c r="F53" s="6"/>
+      <c r="B53" s="3"/>
+      <c r="C53" s="4"/>
+      <c r="D53" s="4"/>
+      <c r="E53" s="4"/>
+      <c r="F53" s="5"/>
     </row>
     <row r="54" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="3" t="s">
+      <c r="A54" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B54" s="4"/>
-      <c r="C54" s="5"/>
-      <c r="D54" s="5"/>
-      <c r="E54" s="5"/>
-      <c r="F54" s="6"/>
+      <c r="B54" s="3"/>
+      <c r="C54" s="4"/>
+      <c r="D54" s="4"/>
+      <c r="E54" s="4"/>
+      <c r="F54" s="5"/>
     </row>
     <row r="55" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="3" t="s">
+      <c r="A55" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B55" s="4"/>
-      <c r="C55" s="5"/>
-      <c r="D55" s="5"/>
-      <c r="E55" s="5"/>
-      <c r="F55" s="6"/>
+      <c r="B55" s="3"/>
+      <c r="C55" s="4"/>
+      <c r="D55" s="4"/>
+      <c r="E55" s="4"/>
+      <c r="F55" s="5"/>
     </row>
     <row r="56" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="3" t="s">
+      <c r="A56" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B56" s="4"/>
-      <c r="C56" s="5"/>
-      <c r="D56" s="5"/>
-      <c r="E56" s="5"/>
-      <c r="F56" s="6"/>
+      <c r="B56" s="3"/>
+      <c r="C56" s="4"/>
+      <c r="D56" s="4"/>
+      <c r="E56" s="4"/>
+      <c r="F56" s="5"/>
     </row>
     <row r="57" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="3" t="s">
+      <c r="A57" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B57" s="4"/>
-      <c r="C57" s="5"/>
-      <c r="D57" s="5"/>
-      <c r="E57" s="5"/>
-      <c r="F57" s="6"/>
+      <c r="B57" s="3"/>
+      <c r="C57" s="4"/>
+      <c r="D57" s="4"/>
+      <c r="E57" s="4"/>
+      <c r="F57" s="5"/>
     </row>
     <row r="58" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="3" t="s">
+      <c r="A58" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B58" s="4"/>
-      <c r="C58" s="5"/>
-      <c r="D58" s="5"/>
-      <c r="E58" s="5"/>
-      <c r="F58" s="6"/>
+      <c r="B58" s="3"/>
+      <c r="C58" s="4"/>
+      <c r="D58" s="4"/>
+      <c r="E58" s="4"/>
+      <c r="F58" s="5"/>
     </row>
     <row r="59" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="3" t="s">
+      <c r="A59" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B59" s="4"/>
-      <c r="C59" s="5"/>
-      <c r="D59" s="5"/>
-      <c r="E59" s="5"/>
-      <c r="F59" s="6"/>
+      <c r="B59" s="3"/>
+      <c r="C59" s="4" t="n">
+        <v>1.01753238315852</v>
+      </c>
+      <c r="D59" s="4" t="n">
+        <v>0.171453571555261</v>
+      </c>
+      <c r="E59" s="4"/>
+      <c r="F59" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="3" t="s">
+      <c r="A60" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B60" s="4"/>
-      <c r="C60" s="5" t="n">
-        <v>1.01753238315852</v>
-      </c>
-      <c r="D60" s="5" t="n">
-        <v>0.171453571555261</v>
-      </c>
-      <c r="E60" s="5"/>
-      <c r="F60" s="6" t="n">
+      <c r="B60" s="3"/>
+      <c r="C60" s="4" t="n">
+        <v>0.639586974070559</v>
+      </c>
+      <c r="D60" s="4" t="n">
+        <v>-0.0236082912318806</v>
+      </c>
+      <c r="E60" s="4"/>
+      <c r="F60" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="3" t="s">
+      <c r="A61" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B61" s="4"/>
-      <c r="C61" s="5" t="n">
-        <v>0.639586974070559</v>
-      </c>
-      <c r="D61" s="5" t="n">
-        <v>-0.0236082912318806</v>
-      </c>
-      <c r="E61" s="5"/>
-      <c r="F61" s="6" t="n">
+      <c r="B61" s="3"/>
+      <c r="C61" s="4" t="n">
+        <v>0.193918025561922</v>
+      </c>
+      <c r="D61" s="4" t="n">
+        <v>0.118069330310758</v>
+      </c>
+      <c r="E61" s="4"/>
+      <c r="F61" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="3" t="s">
+      <c r="A62" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B62" s="4"/>
-      <c r="C62" s="5" t="n">
-        <v>0.193918025561922</v>
-      </c>
-      <c r="D62" s="5" t="n">
-        <v>0.118069330310758</v>
-      </c>
-      <c r="E62" s="5"/>
-      <c r="F62" s="6" t="n">
+      <c r="B62" s="3" t="n">
+        <v>9.92886843827174</v>
+      </c>
+      <c r="C62" s="4" t="n">
+        <v>0.180346617401249</v>
+      </c>
+      <c r="D62" s="4" t="n">
+        <v>0.159205622906741</v>
+      </c>
+      <c r="E62" s="4" t="n">
+        <v>4.10677618069815</v>
+      </c>
+      <c r="F62" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="3" t="s">
+      <c r="A63" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B63" s="4" t="n">
-        <v>9.92886843827174</v>
-      </c>
-      <c r="C63" s="5" t="n">
-        <v>0.180346617401249</v>
-      </c>
-      <c r="D63" s="5" t="n">
-        <v>0.159205622906741</v>
-      </c>
-      <c r="E63" s="5" t="n">
-        <v>4.10677618069815</v>
-      </c>
-      <c r="F63" s="6" t="n">
+      <c r="B63" s="3" t="n">
+        <v>5.70265547896546</v>
+      </c>
+      <c r="C63" s="4" t="n">
+        <v>0.837760702524698</v>
+      </c>
+      <c r="D63" s="4" t="n">
+        <v>0.0200162484840635</v>
+      </c>
+      <c r="E63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="3" t="s">
+      <c r="A64" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B64" s="4" t="n">
-        <v>5.70265547896546</v>
-      </c>
-      <c r="C64" s="5" t="n">
-        <v>0.837760702524698</v>
-      </c>
-      <c r="D64" s="5" t="n">
-        <v>0.0200162484840635</v>
-      </c>
-      <c r="E64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F64" s="6" t="n">
-        <v>0</v>
+      <c r="B64" s="3" t="n">
+        <v>5.5948120833409</v>
+      </c>
+      <c r="C64" s="4" t="n">
+        <v>0.29391530014195</v>
+      </c>
+      <c r="D64" s="4" t="n">
+        <v>0.483825399067665</v>
+      </c>
+      <c r="E64" s="4" t="n">
+        <v>10.8763031839955</v>
+      </c>
+      <c r="F64" s="5" t="n">
+        <v>0.638080653394589</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="3" t="s">
+      <c r="A65" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B65" s="4" t="n">
-        <v>5.5948120833409</v>
-      </c>
-      <c r="C65" s="5" t="n">
-        <v>0.29391530014195</v>
-      </c>
-      <c r="D65" s="5" t="n">
-        <v>0.483825399067665</v>
-      </c>
-      <c r="E65" s="5" t="n">
-        <v>10.8763031839955</v>
-      </c>
-      <c r="F65" s="6" t="n">
-        <v>0.638080653394589</v>
+      <c r="B65" s="3" t="n">
+        <v>5.5254511362268</v>
+      </c>
+      <c r="C65" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="4" t="n">
+        <v>3.32909783989835</v>
+      </c>
+      <c r="F65" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="3" t="s">
+      <c r="A66" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B66" s="4" t="n">
-        <v>5.5254511362268</v>
-      </c>
-      <c r="C66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E66" s="5" t="n">
-        <v>3.32909783989835</v>
-      </c>
-      <c r="F66" s="6" t="n">
-        <v>0</v>
+      <c r="B66" s="3" t="n">
+        <v>5.88983258073456</v>
+      </c>
+      <c r="C66" s="4" t="n">
+        <v>0.0438495569458132</v>
+      </c>
+      <c r="D66" s="4" t="n">
+        <v>0.113637694912077</v>
+      </c>
+      <c r="E66" s="4" t="n">
+        <v>1.81997048696508</v>
+      </c>
+      <c r="F66" s="5" t="n">
+        <v>0.402612224194776</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="3" t="s">
+      <c r="A67" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B67" s="4" t="n">
-        <v>5.88983258073456</v>
-      </c>
-      <c r="C67" s="5" t="n">
-        <v>0.0438495569458132</v>
-      </c>
-      <c r="D67" s="5" t="n">
-        <v>0.113637694912077</v>
-      </c>
-      <c r="E67" s="5" t="n">
-        <v>1.81997048696508</v>
-      </c>
-      <c r="F67" s="6" t="n">
-        <v>0.402612224194776</v>
+      <c r="B67" s="3" t="n">
+        <v>3.69480879364493</v>
+      </c>
+      <c r="C67" s="4" t="n">
+        <v>2.17155454490223</v>
+      </c>
+      <c r="D67" s="4" t="n">
+        <v>0.0526586781501591</v>
+      </c>
+      <c r="E67" s="4" t="n">
+        <v>1.23188405797101</v>
+      </c>
+      <c r="F67" s="5" t="n">
+        <v>10.2964857440561</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="3" t="s">
+      <c r="A68" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B68" s="4" t="n">
-        <v>3.69480879364493</v>
-      </c>
-      <c r="C68" s="5" t="n">
-        <v>2.17155454490223</v>
-      </c>
-      <c r="D68" s="5" t="n">
-        <v>0.0526586781501591</v>
-      </c>
-      <c r="E68" s="5" t="n">
-        <v>1.23188405797101</v>
-      </c>
-      <c r="F68" s="6" t="n">
-        <v>10.2964857440561</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="3" t="s">
+      <c r="B68" s="3" t="n">
+        <v>5.93711027970782</v>
+      </c>
+      <c r="C68" s="4" t="n">
+        <v>3.97004731606623</v>
+      </c>
+      <c r="D68" s="4" t="n">
+        <v>0.431573899720471</v>
+      </c>
+      <c r="E68" s="4" t="n">
+        <v>1.14531138153185</v>
+      </c>
+      <c r="F68" s="5" t="n">
+        <v>1.93232566128478</v>
+      </c>
+    </row>
+    <row r="69" s="7" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B69" s="4" t="n">
-        <v>5.93711027970782</v>
-      </c>
-      <c r="C69" s="5" t="n">
-        <v>3.97004731606623</v>
-      </c>
-      <c r="D69" s="5" t="n">
-        <v>0.431573899720471</v>
-      </c>
-      <c r="E69" s="5" t="n">
-        <v>1.14531138153185</v>
-      </c>
-      <c r="F69" s="6" t="n">
-        <v>1.93232566128478</v>
-      </c>
-    </row>
-    <row r="70" s="8" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="7" t="s">
+      <c r="B69" s="6"/>
+      <c r="C69" s="6"/>
+      <c r="D69" s="6"/>
+      <c r="E69" s="6"/>
+    </row>
+    <row r="70" s="7" customFormat="true" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="B70" s="7"/>
-      <c r="C70" s="7"/>
-      <c r="D70" s="7"/>
-      <c r="E70" s="7"/>
-    </row>
-    <row r="71" s="8" customFormat="true" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B70" s="8"/>
+      <c r="C70" s="8"/>
+      <c r="D70" s="8"/>
+      <c r="E70" s="8"/>
+    </row>
+    <row r="71" s="9" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="B71" s="9"/>
-      <c r="C71" s="9"/>
-      <c r="D71" s="9"/>
-      <c r="E71" s="9"/>
-    </row>
-    <row r="72" s="10" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="10" t="s">
+    </row>
+    <row r="72" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="9" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="73" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="10" t="s">
+    <row r="73" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="9" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="74" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="10" t="s">
+    <row r="74" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="75" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="10" t="s">
+    <row r="75" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="9" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="76" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="10" t="s">
+    <row r="76" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="9" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="77" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="10" t="s">
+    <row r="77" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="9" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="78" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="10" t="s">
+    <row r="78" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="9" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="79" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="10" t="s">
+    <row r="79" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="9" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="80" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="10" t="s">
+    <row r="80" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="9" t="s">
         <v>84</v>
       </c>
     </row>
@@ -1472,31 +1454,16 @@
         <v>85</v>
       </c>
     </row>
-    <row r="82" s="11" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="11" t="s">
+    <row r="82" customFormat="false" ht="18.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="0" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="18.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="0" t="s">
-        <v>87</v>
-      </c>
-    </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="2">
+    <mergeCell ref="A69:E69"/>
     <mergeCell ref="A70:E70"/>
-    <mergeCell ref="A71:E71"/>
-    <mergeCell ref="72:72"/>
-    <mergeCell ref="73:73"/>
-    <mergeCell ref="74:74"/>
-    <mergeCell ref="75:75"/>
-    <mergeCell ref="76:76"/>
-    <mergeCell ref="77:77"/>
-    <mergeCell ref="78:78"/>
-    <mergeCell ref="79:79"/>
-    <mergeCell ref="80:80"/>
-    <mergeCell ref="81:81"/>
-    <mergeCell ref="82:82"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/agriculture 42.xlsx
+++ b/agriculture 42.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
   <si>
     <t xml:space="preserve">Year</t>
   </si>
@@ -239,6 +239,9 @@
   </si>
   <si>
     <t xml:space="preserve">2016-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unit:- </t>
   </si>
   <si>
     <r>
@@ -248,7 +251,6 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Source</t>
     </r>
@@ -258,22 +260,36 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">: EPWRF( Economic and Political Weekly Research Foundation) 1950-2020</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Footnote Description:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">: Telangana:-&gt; On 2 June 2014, Telangana was separated from Andhra Pradesh as the 29th state of India. However Indian Horticulture Database disseminated separate data for both Andhra Pradesh &amp; Telangana in the year 2013-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">:-&gt; Data for Daman and Diu are included under Goa, Daman and Diu for the years 1962-63 To 1979-80.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">:-&gt; Data for Haryana are included under Punjab for the years 1962-63 To 1964-65.</t>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Footnote Description:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Telangana:-&gt; On 2 June 2014, Telangana was separated from Andhra Pradesh as the 29th state of India. However Indian Horticulture Database disseminated separate data for both Andhra Pradesh &amp; Telangana in the year 2013-14</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Data for Daman and Diu are included under Goa, Daman and Diu for the years 1962-63 To 1979-80.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data for Haryana are included under Punjab for the years 1962-63 To 1964-65.</t>
   </si>
   <si>
     <t xml:space="preserve">1962-63 to 2013-14 - Plantation Crops: Coffee: Area:-&gt; Area refers to the total planted area.</t>
@@ -297,10 +313,25 @@
     <t xml:space="preserve">Plantation Crops: Coffee: Yield:-&gt; Coffee Yield is based on plucked area.</t>
   </si>
   <si>
-    <t xml:space="preserve">Source Description:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Directorate of Economics and Statistics, Dept. of Agriculture, Cooperation and Farmers Welfare, Ministry of Agriculture, Govt. of India</t>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Source Description: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Directorate of Economics and Statistics, Dept. of Agriculture, Cooperation and Farmers Welfare, Ministry of Agriculture, Govt. of India</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -312,7 +343,7 @@
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="0.00"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -343,11 +374,30 @@
       <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -406,7 +456,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -431,16 +481,24 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -468,8 +526,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F1048576"/>
-  <sheetFormatPr defaultColWidth="10.78515625" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:F83"/>
+  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="14.42"/>
   </cols>
@@ -1381,89 +1439,153 @@
         <v>1.93232566128478</v>
       </c>
     </row>
-    <row r="69" s="7" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="6" t="s">
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B69" s="6"/>
-      <c r="C69" s="6"/>
-      <c r="D69" s="6"/>
-      <c r="E69" s="6"/>
-    </row>
-    <row r="70" s="7" customFormat="true" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="8" t="s">
+      <c r="B69" s="2"/>
+      <c r="C69" s="2"/>
+      <c r="D69" s="2"/>
+      <c r="E69" s="2"/>
+      <c r="F69" s="2"/>
+    </row>
+    <row r="70" s="7" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="B70" s="8"/>
-      <c r="C70" s="8"/>
-      <c r="D70" s="8"/>
-      <c r="E70" s="8"/>
-    </row>
-    <row r="71" s="9" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="9" t="s">
+      <c r="B70" s="6"/>
+      <c r="C70" s="6"/>
+      <c r="D70" s="6"/>
+      <c r="E70" s="6"/>
+      <c r="F70" s="6"/>
+    </row>
+    <row r="71" s="7" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="8" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="72" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B71" s="8"/>
+      <c r="C71" s="8"/>
+      <c r="D71" s="8"/>
+      <c r="E71" s="8"/>
+      <c r="F71" s="8"/>
+    </row>
+    <row r="72" s="10" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="9" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="73" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B72" s="9"/>
+      <c r="C72" s="9"/>
+      <c r="D72" s="9"/>
+      <c r="E72" s="9"/>
+      <c r="F72" s="9"/>
+    </row>
+    <row r="73" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="9" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="74" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B73" s="9"/>
+      <c r="C73" s="9"/>
+      <c r="D73" s="9"/>
+      <c r="E73" s="9"/>
+      <c r="F73" s="9"/>
+    </row>
+    <row r="74" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="9" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="75" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B74" s="9"/>
+      <c r="C74" s="9"/>
+      <c r="D74" s="9"/>
+      <c r="E74" s="9"/>
+      <c r="F74" s="9"/>
+    </row>
+    <row r="75" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="9" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="76" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B75" s="9"/>
+      <c r="C75" s="9"/>
+      <c r="D75" s="9"/>
+      <c r="E75" s="9"/>
+      <c r="F75" s="9"/>
+    </row>
+    <row r="76" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="9" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="77" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B76" s="9"/>
+      <c r="C76" s="9"/>
+      <c r="D76" s="9"/>
+      <c r="E76" s="9"/>
+      <c r="F76" s="9"/>
+    </row>
+    <row r="77" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="9" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="78" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B77" s="9"/>
+      <c r="C77" s="9"/>
+      <c r="D77" s="9"/>
+      <c r="E77" s="9"/>
+      <c r="F77" s="9"/>
+    </row>
+    <row r="78" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="9" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="79" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B78" s="9"/>
+      <c r="C78" s="9"/>
+      <c r="D78" s="9"/>
+      <c r="E78" s="9"/>
+      <c r="F78" s="9"/>
+    </row>
+    <row r="79" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="9" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="80" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B79" s="9"/>
+      <c r="C79" s="9"/>
+      <c r="D79" s="9"/>
+      <c r="E79" s="9"/>
+      <c r="F79" s="9"/>
+    </row>
+    <row r="80" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="9" t="s">
         <v>84</v>
       </c>
+      <c r="B80" s="9"/>
+      <c r="C80" s="9"/>
+      <c r="D80" s="9"/>
+      <c r="E80" s="9"/>
+      <c r="F80" s="9"/>
     </row>
     <row r="81" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="10" t="s">
+      <c r="A81" s="11" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="82" customFormat="false" ht="18.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="0" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="B81" s="11"/>
+      <c r="C81" s="11"/>
+      <c r="D81" s="11"/>
+      <c r="E81" s="11"/>
+      <c r="F81" s="11"/>
+    </row>
+    <row r="82" s="12" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="83" customFormat="false" ht="18.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A69:E69"/>
-    <mergeCell ref="A70:E70"/>
+  <mergeCells count="13">
+    <mergeCell ref="A69:F69"/>
+    <mergeCell ref="A70:F70"/>
+    <mergeCell ref="A71:F71"/>
+    <mergeCell ref="A72:F72"/>
+    <mergeCell ref="A73:F73"/>
+    <mergeCell ref="A74:F74"/>
+    <mergeCell ref="A75:F75"/>
+    <mergeCell ref="A76:F76"/>
+    <mergeCell ref="A77:F77"/>
+    <mergeCell ref="A78:F78"/>
+    <mergeCell ref="A79:F79"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A81:F81"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/agriculture 42.xlsx
+++ b/agriculture 42.xlsx
@@ -241,7 +241,7 @@
     <t xml:space="preserve">2016-17</t>
   </si>
   <si>
-    <t xml:space="preserve">Unit:- </t>
+    <t xml:space="preserve">Unit:- Percentage(%)</t>
   </si>
   <si>
     <r>
@@ -251,6 +251,7 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Source</t>
     </r>
@@ -260,6 +261,7 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">: EPWRF( Economic and Political Weekly Research Foundation) 1950-2020</t>
     </r>
@@ -272,6 +274,7 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Footnote Description:</t>
     </r>
@@ -281,6 +284,7 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> Telangana:-&gt; On 2 June 2014, Telangana was separated from Andhra Pradesh as the 29th state of India. However Indian Horticulture Database disseminated separate data for both Andhra Pradesh &amp; Telangana in the year 2013-14</t>
     </r>
@@ -320,6 +324,7 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Source Description: </t>
     </r>
@@ -329,6 +334,7 @@
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Directorate of Economics and Statistics, Dept. of Agriculture, Cooperation and Farmers Welfare, Ministry of Agriculture, Govt. of India</t>
     </r>
@@ -343,7 +349,7 @@
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="0.00"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -374,19 +380,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -398,6 +391,7 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -456,7 +450,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -481,24 +475,16 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -527,7 +513,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F83"/>
-  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.8125" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="14.42"/>
   </cols>
@@ -1469,107 +1455,62 @@
       <c r="E71" s="8"/>
       <c r="F71" s="8"/>
     </row>
-    <row r="72" s="10" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="72" s="9" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="B72" s="9"/>
-      <c r="C72" s="9"/>
-      <c r="D72" s="9"/>
-      <c r="E72" s="9"/>
-      <c r="F72" s="9"/>
-    </row>
-    <row r="73" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="73" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="B73" s="9"/>
-      <c r="C73" s="9"/>
-      <c r="D73" s="9"/>
-      <c r="E73" s="9"/>
-      <c r="F73" s="9"/>
-    </row>
-    <row r="74" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="74" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="B74" s="9"/>
-      <c r="C74" s="9"/>
-      <c r="D74" s="9"/>
-      <c r="E74" s="9"/>
-      <c r="F74" s="9"/>
-    </row>
-    <row r="75" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="75" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="B75" s="9"/>
-      <c r="C75" s="9"/>
-      <c r="D75" s="9"/>
-      <c r="E75" s="9"/>
-      <c r="F75" s="9"/>
-    </row>
-    <row r="76" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="76" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="B76" s="9"/>
-      <c r="C76" s="9"/>
-      <c r="D76" s="9"/>
-      <c r="E76" s="9"/>
-      <c r="F76" s="9"/>
-    </row>
-    <row r="77" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="77" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="B77" s="9"/>
-      <c r="C77" s="9"/>
-      <c r="D77" s="9"/>
-      <c r="E77" s="9"/>
-      <c r="F77" s="9"/>
-    </row>
-    <row r="78" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="78" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="B78" s="9"/>
-      <c r="C78" s="9"/>
-      <c r="D78" s="9"/>
-      <c r="E78" s="9"/>
-      <c r="F78" s="9"/>
-    </row>
-    <row r="79" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="79" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="B79" s="9"/>
-      <c r="C79" s="9"/>
-      <c r="D79" s="9"/>
-      <c r="E79" s="9"/>
-      <c r="F79" s="9"/>
-    </row>
-    <row r="80" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="80" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="B80" s="9"/>
-      <c r="C80" s="9"/>
-      <c r="D80" s="9"/>
-      <c r="E80" s="9"/>
-      <c r="F80" s="9"/>
-    </row>
-    <row r="81" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="11" t="s">
+    </row>
+    <row r="81" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="B81" s="11"/>
-      <c r="C81" s="11"/>
-      <c r="D81" s="11"/>
-      <c r="E81" s="11"/>
-      <c r="F81" s="11"/>
-    </row>
-    <row r="82" s="12" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+      <c r="B81" s="10"/>
+      <c r="C81" s="10"/>
+      <c r="D81" s="10"/>
+      <c r="E81" s="10"/>
+      <c r="F81" s="10"/>
+    </row>
+    <row r="82" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="83" customFormat="false" ht="18.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="13">

--- a/agriculture 42.xlsx
+++ b/agriculture 42.xlsx
@@ -241,7 +241,7 @@
     <t xml:space="preserve">2016-17</t>
   </si>
   <si>
-    <t xml:space="preserve">Unit:- Percentage(%)</t>
+    <t xml:space="preserve">Unit:- Percentage (%)</t>
   </si>
   <si>
     <r>
@@ -513,7 +513,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F83"/>
-  <sheetFormatPr defaultColWidth="10.8125" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.82421875" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="14.42"/>
   </cols>
